--- a/ThucHanhApp/static/tonkho_mau.xlsx
+++ b/ThucHanhApp/static/tonkho_mau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LaptrinhGis\ThucHanh\ThucHanhApp\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC12751B-41AE-4244-93D6-41763DE2BAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743BC969-7DA6-4632-B0E9-447D6684BB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,10 +31,10 @@
     <t>Số lượng</t>
   </si>
   <si>
-    <t>FamilyMart Cầu Giấy</t>
+    <t>Circle K Trần Hưng Đạo</t>
   </si>
   <si>
-    <t>Khăn giấy Kleenex</t>
+    <t>Mì tôm hảo hảo</t>
   </si>
 </sst>
 </file>
@@ -411,5 +411,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ThucHanhApp/static/tonkho_mau.xlsx
+++ b/ThucHanhApp/static/tonkho_mau.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LaptrinhGis\ThucHanh\ThucHanhApp\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743BC969-7DA6-4632-B0E9-447D6684BB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4334CC9D-7642-46C4-A915-B6873F97E041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
     <t>Circle K Trần Hưng Đạo</t>
   </si>
   <si>
-    <t>Mì tôm hảo hảo</t>
+    <t>Coca Cola 330ml</t>
   </si>
 </sst>
 </file>
@@ -406,7 +406,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
